--- a/courses/3/mapo/dist/Учебный_план_Моделирование_и_анализ_программного_обеспечения.xlsx
+++ b/courses/3/mapo/dist/Учебный_план_Моделирование_и_анализ_программного_обеспечения.xlsx
@@ -160,7 +160,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Минуты</t>
+          <t xml:space="preserve">Часы</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -191,7 +191,7 @@
         </is>
       </c>
       <c r="D6" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -221,7 +221,7 @@
         </is>
       </c>
       <c r="D7" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
@@ -251,7 +251,7 @@
         </is>
       </c>
       <c r="D8" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -281,7 +281,7 @@
         </is>
       </c>
       <c r="D9" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -311,7 +311,7 @@
         </is>
       </c>
       <c r="D10" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -341,7 +341,7 @@
         </is>
       </c>
       <c r="D11" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -371,7 +371,7 @@
         </is>
       </c>
       <c r="D12" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="D13" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -431,7 +431,7 @@
         </is>
       </c>
       <c r="D14" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="D15" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="D16" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="D17" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="D18" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="D19" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D20" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="D21" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D22" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="D23" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="D24" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="D25" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="D26" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="D27" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="D28" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="D29" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="D31" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="D32" s="6">
-        <v>2880</v>
+        <v>64</v>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
